--- a/data/processed/harmonization/Carbon__Particulate_organic_matter_carbon/10.15485_3024414/10.15485_3024414_soil_Carbon__Particulate_organic_matter_carbon.xlsx
+++ b/data/processed/harmonization/Carbon__Particulate_organic_matter_carbon/10.15485_3024414/10.15485_3024414_soil_Carbon__Particulate_organic_matter_carbon.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="43" customWidth="1" min="7" max="7"/>
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Control:2</t>
+          <t>Control:1:80-90</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -575,12 +575,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Control:6</t>
+          <t>Control:1:40-50</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -626,12 +626,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Control:9</t>
+          <t>Control:1:10-20</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Warmed:12</t>
+          <t>Warmed:2:80-90</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -728,12 +728,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Warmed:16</t>
+          <t>Warmed:2:40-50</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Warmed:19</t>
+          <t>Warmed:2:10-20</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Control:22</t>
+          <t>Control:3:80-90</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Control:26</t>
+          <t>Control:3:40-50</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Control:29</t>
+          <t>Control:3:10-20</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -983,12 +983,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Warmed:32</t>
+          <t>Warmed:4:80-90</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Warmed:36</t>
+          <t>Warmed:4:40-50</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Warmed:39</t>
+          <t>Warmed:4:10-20</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Control:42</t>
+          <t>Control:5:80-90</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Control:46</t>
+          <t>Control:5:40-50</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Control:49</t>
+          <t>Control:5:10-20</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Warmed:52</t>
+          <t>Warmed:6:80-90</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Warmed:56</t>
+          <t>Warmed:6:40-50</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Warmed:59</t>
+          <t>Warmed:6:10-20</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Control:2</t>
+          <t>Control:1:80-90</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Control:6</t>
+          <t>Control:1:40-50</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Control:9</t>
+          <t>Control:1:10-20</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Warmed:12</t>
+          <t>Warmed:2:80-90</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Warmed:16</t>
+          <t>Warmed:2:40-50</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Warmed:19</t>
+          <t>Warmed:2:10-20</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Control:22</t>
+          <t>Control:3:80-90</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Control:26</t>
+          <t>Control:3:40-50</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Control:29</t>
+          <t>Control:3:10-20</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Warmed:32</t>
+          <t>Warmed:4:80-90</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Warmed:36</t>
+          <t>Warmed:4:40-50</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Warmed:39</t>
+          <t>Warmed:4:10-20</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Control:42</t>
+          <t>Control:5:80-90</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Control:46</t>
+          <t>Control:5:40-50</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Control:49</t>
+          <t>Control:5:10-20</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Warmed:52</t>
+          <t>Warmed:6:80-90</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Warmed:56</t>
+          <t>Warmed:6:40-50</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Warmed:59</t>
+          <t>Warmed:6:10-20</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Control:2</t>
+          <t>Control:1:80-90</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Control:6</t>
+          <t>Control:1:40-50</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Control:9</t>
+          <t>Control:1:10-20</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2513,12 +2513,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Warmed:12</t>
+          <t>Warmed:2:80-90</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Warmed:16</t>
+          <t>Warmed:2:40-50</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2615,12 +2615,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Warmed:19</t>
+          <t>Warmed:2:10-20</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2666,12 +2666,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Control:22</t>
+          <t>Control:3:80-90</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Control:26</t>
+          <t>Control:3:40-50</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2768,12 +2768,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Control:29</t>
+          <t>Control:3:10-20</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Warmed:32</t>
+          <t>Warmed:4:80-90</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Warmed:36</t>
+          <t>Warmed:4:40-50</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Warmed:39</t>
+          <t>Warmed:4:10-20</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Control:42</t>
+          <t>Control:5:80-90</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Control:46</t>
+          <t>Control:5:40-50</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Control:49</t>
+          <t>Control:5:10-20</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3125,12 +3125,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Warmed:52</t>
+          <t>Warmed:6:80-90</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Warmed:56</t>
+          <t>Warmed:6:40-50</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Warmed:59</t>
+          <t>Warmed:6:10-20</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Control:2</t>
+          <t>Control:1:80-90</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Control:6</t>
+          <t>Control:1:40-50</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Control:9</t>
+          <t>Control:1:10-20</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Warmed:12</t>
+          <t>Warmed:2:80-90</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Warmed:16</t>
+          <t>Warmed:2:40-50</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3533,12 +3533,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Warmed:19</t>
+          <t>Warmed:2:10-20</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Control:22</t>
+          <t>Control:3:80-90</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Control:26</t>
+          <t>Control:3:40-50</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Control:29</t>
+          <t>Control:3:10-20</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Warmed:32</t>
+          <t>Warmed:4:80-90</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3788,12 +3788,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Warmed:36</t>
+          <t>Warmed:4:40-50</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Warmed:39</t>
+          <t>Warmed:4:10-20</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Control:42</t>
+          <t>Control:5:80-90</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Control:46</t>
+          <t>Control:5:40-50</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Control:49</t>
+          <t>Control:5:10-20</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4043,12 +4043,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Warmed:52</t>
+          <t>Warmed:6:80-90</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4094,12 +4094,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Warmed:56</t>
+          <t>Warmed:6:40-50</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Warmed:59</t>
+          <t>Warmed:6:10-20</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
